--- a/currentbuild/StructureDefinition-lmdi-medicationrequest.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medicationrequest.xlsx
@@ -1092,7 +1092,7 @@
     <t>MedicationRequest.courseOfTherapyType</t>
   </si>
   <si>
-    <t>continuous | acute | seasonal</t>
+    <t>Type behandlingsforløp (continuous | acute | seasonal)</t>
   </si>
   <si>
     <t>The description of the overall patte3rn of the administration of the medication to the patient.</t>

--- a/currentbuild/StructureDefinition-lmdi-medicationrequest.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medicationrequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.8</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/StructureDefinition-lmdi-medicationrequest.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medicationrequest.xlsx
@@ -472,7 +472,7 @@
     <t>Doseendring i prosent</t>
   </si>
   <si>
-    <t>Doseendring i prosent, sammenlignet med opprinnelig dosering. Spesielt relevant ved kjemoterapi. Kan ha verdier fra 0. Ved vanlig dose uten endring er doseendring 100 (%). Enhet skal være prosent.</t>
+    <t>Doseendring i prosent, sammenlignet med opprinnelig dosering. Spesielt relevant ved kjemoterapi. En normal dose, uten modifiseringer, er 100%. Kan ha verdier fra 0. Enhet skal være prosent.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1

--- a/currentbuild/StructureDefinition-lmdi-medicationrequest.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medicationrequest.xlsx
@@ -469,7 +469,7 @@
 </t>
   </si>
   <si>
-    <t>Doseendring i prosent</t>
+    <t>Doseendring i prosent (100% = normal umodifisert dose)</t>
   </si>
   <si>
     <t>Doseendring i prosent, sammenlignet med opprinnelig dosering. Spesielt relevant ved kjemoterapi. En normal dose, uten modifiseringer, er 100%. Kan ha verdier fra 0. Enhet skal være prosent.</t>

--- a/currentbuild/StructureDefinition-lmdi-medicationrequest.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medicationrequest.xlsx
@@ -469,7 +469,7 @@
 </t>
   </si>
   <si>
-    <t>Doseendring i prosent (100% = normal umodifisert dose)</t>
+    <t>Doseendring i prosent (100% = umodifisert dose)</t>
   </si>
   <si>
     <t>Doseendring i prosent, sammenlignet med opprinnelig dosering. Spesielt relevant ved kjemoterapi. En normal dose, uten modifiseringer, er 100%. Kan ha verdier fra 0. Enhet skal være prosent.</t>

--- a/currentbuild/StructureDefinition-lmdi-medicationrequest.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medicationrequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/StructureDefinition-lmdi-medicationrequest.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medicationrequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.1.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>90</v>

--- a/currentbuild/StructureDefinition-lmdi-medicationrequest.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medicationrequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.3</t>
+    <t>1.1.4</t>
   </si>
   <si>
     <t>Name</t>
